--- a/Excel/StockQuotation (8).xlsx
+++ b/Excel/StockQuotation (8).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>03/02/23 13:00:16</v>
+        <v>07/02/23 23:30:43</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>374.16</v>
+        <v>372.26</v>
       </c>
       <c r="B7" t="str">
-        <v>-2.19 (-0.5819%)</v>
+        <v>-1.5 (-0.4013%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>376.03</v>
+        <v>374.2</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>373.53</v>
+        <v>370.84</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>153245912</v>
+        <v>415445555</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>1712085722.81</v>
+        <v>3395647413.95</v>
       </c>
     </row>
     <row r="9">
@@ -534,46 +534,46 @@
         <v>-</v>
       </c>
       <c r="C11">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="D11">
         <v>-0.02</v>
       </c>
       <c r="E11">
-        <v>-0.6493506493506493</v>
+        <v>-0.6451612903225806</v>
       </c>
       <c r="F11">
+        <v>3.1</v>
+      </c>
+      <c r="G11">
+        <v>3.12</v>
+      </c>
+      <c r="H11">
+        <v>3.06</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>47860704</v>
+      </c>
+      <c r="L11">
+        <v>148095.61584</v>
+      </c>
+      <c r="M11">
+        <v>10938600</v>
+      </c>
+      <c r="N11">
+        <v>3.06</v>
+      </c>
+      <c r="O11">
         <v>3.08</v>
       </c>
-      <c r="G11">
-        <v>3.08</v>
-      </c>
-      <c r="H11">
-        <v>3.04</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>32807300</v>
-      </c>
-      <c r="L11">
-        <v>100509.9188</v>
-      </c>
-      <c r="M11">
-        <v>17097600</v>
-      </c>
-      <c r="N11">
-        <v>3.04</v>
-      </c>
-      <c r="O11">
-        <v>3.06</v>
-      </c>
       <c r="P11">
-        <v>1037400</v>
+        <v>307300</v>
       </c>
     </row>
     <row r="12">
@@ -584,46 +584,46 @@
         <v>-</v>
       </c>
       <c r="C12">
+        <v>73.5</v>
+      </c>
+      <c r="D12">
+        <v>-0.25</v>
+      </c>
+      <c r="E12">
+        <v>-0.3389830508474576</v>
+      </c>
+      <c r="F12">
+        <v>73.5</v>
+      </c>
+      <c r="G12">
+        <v>74</v>
+      </c>
+      <c r="H12">
+        <v>73.25</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>19882884</v>
+      </c>
+      <c r="L12">
+        <v>1462189.4985</v>
+      </c>
+      <c r="M12">
+        <v>5942900</v>
+      </c>
+      <c r="N12">
+        <v>73.5</v>
+      </c>
+      <c r="O12">
         <v>73.75</v>
       </c>
-      <c r="D12">
-        <v>-0.75</v>
-      </c>
-      <c r="E12">
-        <v>-1.0067114093959733</v>
-      </c>
-      <c r="F12">
-        <v>74</v>
-      </c>
-      <c r="G12">
-        <v>74.25</v>
-      </c>
-      <c r="H12">
-        <v>73.75</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>15849880</v>
-      </c>
-      <c r="L12">
-        <v>1172900.6285</v>
-      </c>
-      <c r="M12">
-        <v>3667400</v>
-      </c>
-      <c r="N12">
-        <v>73.75</v>
-      </c>
-      <c r="O12">
-        <v>74</v>
-      </c>
       <c r="P12">
-        <v>1404700</v>
+        <v>439300</v>
       </c>
     </row>
     <row r="13">
@@ -634,19 +634,19 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="D13">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E13">
-        <v>-0.5434782608695652</v>
+        <v>1.6483516483516483</v>
       </c>
       <c r="F13">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G13">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H13">
         <v>1.82</v>
@@ -658,22 +658,22 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>45800</v>
+        <v>173315</v>
       </c>
       <c r="L13">
-        <v>83.969</v>
+        <v>319.28445</v>
       </c>
       <c r="M13">
-        <v>35800</v>
+        <v>16600</v>
       </c>
       <c r="N13">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="O13">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="P13">
-        <v>45400</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="14">
@@ -684,23 +684,23 @@
         <v>-</v>
       </c>
       <c r="C14">
+        <v>0.44</v>
+      </c>
+      <c r="D14">
+        <v>0.03</v>
+      </c>
+      <c r="E14">
+        <v>7.317073170731708</v>
+      </c>
+      <c r="F14">
+        <v>0.42</v>
+      </c>
+      <c r="G14">
+        <v>0.46</v>
+      </c>
+      <c r="H14">
         <v>0.41</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0.41</v>
-      </c>
-      <c r="G14">
-        <v>0.42</v>
-      </c>
-      <c r="H14">
-        <v>0.4</v>
-      </c>
       <c r="I14">
         <v>0</v>
       </c>
@@ -708,22 +708,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>17118001</v>
+        <v>158162818</v>
       </c>
       <c r="L14">
-        <v>7016.0494100000005</v>
+        <v>69981.95081000001</v>
       </c>
       <c r="M14">
-        <v>24153500</v>
+        <v>10628000</v>
       </c>
       <c r="N14">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="O14">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="P14">
-        <v>2997100</v>
+        <v>7799100</v>
       </c>
     </row>
     <row r="15">
@@ -734,22 +734,22 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="D15">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E15">
-        <v>0.6944444444444444</v>
+        <v>2.0689655172413794</v>
       </c>
       <c r="F15">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="G15">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="H15">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -758,22 +758,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>906455</v>
+        <v>9344082</v>
       </c>
       <c r="L15">
-        <v>13123.8895</v>
+        <v>136141.3224</v>
       </c>
       <c r="M15">
-        <v>162600</v>
+        <v>153200</v>
       </c>
       <c r="N15">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="O15">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="P15">
-        <v>61600</v>
+        <v>137100</v>
       </c>
     </row>
     <row r="16">
@@ -784,13 +784,13 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>9.75</v>
+        <v>9.6</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>-1.5384615384615385</v>
       </c>
       <c r="F16">
         <v>9.7</v>
@@ -799,31 +799,31 @@
         <v>9.75</v>
       </c>
       <c r="H16">
+        <v>9.55</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>58793587</v>
+      </c>
+      <c r="L16">
+        <v>565334.3098500001</v>
+      </c>
+      <c r="M16">
+        <v>1211000</v>
+      </c>
+      <c r="N16">
+        <v>9.6</v>
+      </c>
+      <c r="O16">
         <v>9.65</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>8532159</v>
-      </c>
-      <c r="L16">
-        <v>82777.6208</v>
-      </c>
-      <c r="M16">
-        <v>4542200</v>
-      </c>
-      <c r="N16">
-        <v>9.7</v>
-      </c>
-      <c r="O16">
-        <v>9.75</v>
-      </c>
       <c r="P16">
-        <v>3210100</v>
+        <v>3215400</v>
       </c>
     </row>
     <row r="17">
@@ -837,19 +837,19 @@
         <v>0.95</v>
       </c>
       <c r="D17">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>-5.9405940594059405</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H17">
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -858,22 +858,22 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>49231161</v>
+        <v>11804761</v>
       </c>
       <c r="L17">
-        <v>46777.93466</v>
+        <v>11197.88796</v>
       </c>
       <c r="M17">
-        <v>4838000</v>
+        <v>1582900</v>
       </c>
       <c r="N17">
+        <v>0.94</v>
+      </c>
+      <c r="O17">
         <v>0.95</v>
       </c>
-      <c r="O17">
-        <v>0.96</v>
-      </c>
       <c r="P17">
-        <v>1124000</v>
+        <v>623000</v>
       </c>
     </row>
     <row r="18">
@@ -884,22 +884,22 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="D18">
         <v>-0.05</v>
       </c>
       <c r="E18">
-        <v>-0.591715976331361</v>
+        <v>-0.6024096385542169</v>
       </c>
       <c r="F18">
+        <v>8.3</v>
+      </c>
+      <c r="G18">
         <v>8.4</v>
       </c>
-      <c r="G18">
-        <v>8.45</v>
-      </c>
       <c r="H18">
-        <v>8.4</v>
+        <v>8.2</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -908,22 +908,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>6616794</v>
+        <v>52782066</v>
       </c>
       <c r="L18">
-        <v>55847.0761</v>
+        <v>436595.46095</v>
       </c>
       <c r="M18">
-        <v>5078500</v>
+        <v>267700</v>
       </c>
       <c r="N18">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="O18">
-        <v>8.45</v>
+        <v>8.3</v>
       </c>
       <c r="P18">
-        <v>1630800</v>
+        <v>1769900</v>
       </c>
     </row>
     <row r="19">
@@ -937,16 +937,16 @@
         <v>3.9</v>
       </c>
       <c r="D19">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.5154639175257731</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="G19">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="H19">
         <v>3.88</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>1184302</v>
+        <v>1226642</v>
       </c>
       <c r="L19">
-        <v>4603.9218</v>
+        <v>4779.416139999999</v>
       </c>
       <c r="M19">
-        <v>294500</v>
+        <v>868800</v>
       </c>
       <c r="N19">
         <v>3.88</v>
@@ -973,7 +973,7 @@
         <v>3.9</v>
       </c>
       <c r="P19">
-        <v>701000</v>
+        <v>308700</v>
       </c>
     </row>
     <row r="20">
@@ -984,46 +984,46 @@
         <v>-</v>
       </c>
       <c r="C20">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>13</v>
+      </c>
+      <c r="G20">
         <v>13.1</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>13.2</v>
-      </c>
-      <c r="G20">
-        <v>13.2</v>
-      </c>
       <c r="H20">
+        <v>12.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>1248511</v>
+      </c>
+      <c r="L20">
+        <v>16126.752</v>
+      </c>
+      <c r="M20">
+        <v>60000</v>
+      </c>
+      <c r="N20">
+        <v>12.9</v>
+      </c>
+      <c r="O20">
         <v>13</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>444546</v>
-      </c>
-      <c r="L20">
-        <v>5831.7126</v>
-      </c>
-      <c r="M20">
-        <v>168400</v>
-      </c>
-      <c r="N20">
-        <v>13</v>
-      </c>
-      <c r="O20">
-        <v>13.1</v>
-      </c>
       <c r="P20">
-        <v>234600</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="21">
@@ -1034,7 +1034,7 @@
         <v>-</v>
       </c>
       <c r="C21">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1043,14 +1043,14 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="G21">
+        <v>15.2</v>
+      </c>
+      <c r="H21">
         <v>14.8</v>
       </c>
-      <c r="H21">
-        <v>14.7</v>
-      </c>
       <c r="I21">
         <v>0</v>
       </c>
@@ -1058,22 +1058,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>508393</v>
+        <v>2849592</v>
       </c>
       <c r="L21">
-        <v>7516.0815</v>
+        <v>42696.6472</v>
       </c>
       <c r="M21">
-        <v>188800</v>
+        <v>142800</v>
       </c>
       <c r="N21">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="O21">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="P21">
-        <v>123500</v>
+        <v>114900</v>
       </c>
     </row>
     <row r="22">
@@ -1084,22 +1084,22 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>21.3</v>
+        <v>20.7</v>
       </c>
       <c r="D22">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E22">
-        <v>0.4716981132075472</v>
+        <v>-0.9569377990430622</v>
       </c>
       <c r="F22">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="G22">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="H22">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1108,22 +1108,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>1299710</v>
+        <v>5033514</v>
       </c>
       <c r="L22">
-        <v>27678.966</v>
+        <v>104421.0835</v>
       </c>
       <c r="M22">
-        <v>134500</v>
+        <v>167300</v>
       </c>
       <c r="N22">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="O22">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="P22">
-        <v>109800</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="23">
@@ -1134,22 +1134,22 @@
         <v>-</v>
       </c>
       <c r="C23">
+        <v>18.3</v>
+      </c>
+      <c r="D23">
+        <v>-0.3</v>
+      </c>
+      <c r="E23">
+        <v>-1.6129032258064515</v>
+      </c>
+      <c r="F23">
+        <v>18.6</v>
+      </c>
+      <c r="G23">
         <v>18.7</v>
       </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
-      <c r="E23">
-        <v>0.5376344086021505</v>
-      </c>
-      <c r="F23">
-        <v>18.9</v>
-      </c>
-      <c r="G23">
-        <v>19</v>
-      </c>
       <c r="H23">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1158,22 +1158,22 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>976661</v>
+        <v>2231293</v>
       </c>
       <c r="L23">
-        <v>18309.578</v>
+        <v>40973.5248</v>
       </c>
       <c r="M23">
-        <v>144400</v>
+        <v>130400</v>
       </c>
       <c r="N23">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="O23">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="P23">
-        <v>84300</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="24">
@@ -1193,7 +1193,7 @@
         <v>2.0408163265306123</v>
       </c>
       <c r="F24">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="G24">
         <v>0.5</v>
@@ -1208,13 +1208,13 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>178200</v>
+        <v>2311200</v>
       </c>
       <c r="L24">
-        <v>87.547</v>
+        <v>1153.77992</v>
       </c>
       <c r="M24">
-        <v>1516400</v>
+        <v>1815300</v>
       </c>
       <c r="N24">
         <v>0.49</v>
@@ -1223,7 +1223,7 @@
         <v>0.5</v>
       </c>
       <c r="P24">
-        <v>2887100</v>
+        <v>3426700</v>
       </c>
     </row>
     <row r="25">
@@ -1233,44 +1233,44 @@
       <c r="B25" t="str">
         <v>-</v>
       </c>
-      <c r="C25" t="str">
-        <v>-</v>
-      </c>
-      <c r="D25" t="str">
-        <v>-</v>
-      </c>
-      <c r="E25" t="str">
-        <v>-</v>
-      </c>
-      <c r="F25" t="str">
-        <v>-</v>
-      </c>
-      <c r="G25" t="str">
-        <v>-</v>
-      </c>
-      <c r="H25" t="str">
-        <v>-</v>
-      </c>
-      <c r="I25" t="str">
-        <v>-</v>
-      </c>
-      <c r="J25" t="str">
-        <v>-</v>
-      </c>
-      <c r="K25" t="str">
-        <v>-</v>
-      </c>
-      <c r="L25" t="str">
-        <v>-</v>
+      <c r="C25">
+        <v>248</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>0.8130081300813008</v>
+      </c>
+      <c r="F25">
+        <v>248</v>
+      </c>
+      <c r="G25">
+        <v>248</v>
+      </c>
+      <c r="H25">
+        <v>248</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>101</v>
+      </c>
+      <c r="L25">
+        <v>25.048</v>
       </c>
       <c r="M25">
         <v>100</v>
       </c>
       <c r="N25">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O25">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -1284,46 +1284,46 @@
         <v>-</v>
       </c>
       <c r="C26">
+        <v>1.93</v>
+      </c>
+      <c r="D26">
+        <v>-0.03</v>
+      </c>
+      <c r="E26">
+        <v>-1.530612244897959</v>
+      </c>
+      <c r="F26">
+        <v>1.94</v>
+      </c>
+      <c r="G26">
+        <v>1.98</v>
+      </c>
+      <c r="H26">
         <v>1.9</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>12027803</v>
+      </c>
+      <c r="L26">
+        <v>23381.7872</v>
+      </c>
+      <c r="M26">
+        <v>299700</v>
+      </c>
+      <c r="N26">
         <v>1.91</v>
       </c>
-      <c r="G26">
-        <v>1.91</v>
-      </c>
-      <c r="H26">
-        <v>1.89</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>655400</v>
-      </c>
-      <c r="L26">
-        <v>1244.966</v>
-      </c>
-      <c r="M26">
-        <v>117600</v>
-      </c>
-      <c r="N26">
-        <v>1.89</v>
-      </c>
       <c r="O26">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="P26">
-        <v>148700</v>
+        <v>155300</v>
       </c>
     </row>
     <row r="27">
@@ -1384,22 +1384,22 @@
         <v>-</v>
       </c>
       <c r="C28">
+        <v>3.56</v>
+      </c>
+      <c r="D28">
+        <v>0.04</v>
+      </c>
+      <c r="E28">
+        <v>1.1363636363636365</v>
+      </c>
+      <c r="F28">
+        <v>3.56</v>
+      </c>
+      <c r="G28">
         <v>3.58</v>
       </c>
-      <c r="D28">
-        <v>0.12</v>
-      </c>
-      <c r="E28">
-        <v>3.468208092485549</v>
-      </c>
-      <c r="F28">
-        <v>3.46</v>
-      </c>
-      <c r="G28">
-        <v>3.6</v>
-      </c>
       <c r="H28">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1408,22 +1408,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>5314524</v>
+        <v>1176916</v>
       </c>
       <c r="L28">
-        <v>18871.75614</v>
+        <v>4173.16084</v>
       </c>
       <c r="M28">
-        <v>167300</v>
+        <v>93000</v>
       </c>
       <c r="N28">
+        <v>3.54</v>
+      </c>
+      <c r="O28">
         <v>3.56</v>
       </c>
-      <c r="O28">
-        <v>3.58</v>
-      </c>
       <c r="P28">
-        <v>115800</v>
+        <v>156500</v>
       </c>
     </row>
     <row r="29">
@@ -1434,22 +1434,22 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>-1.8691588785046729</v>
       </c>
       <c r="F29">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G29">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H29">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1458,22 +1458,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>41400</v>
+        <v>631423</v>
       </c>
       <c r="L29">
-        <v>87.77</v>
+        <v>1310.81764</v>
       </c>
       <c r="M29">
-        <v>2300</v>
+        <v>24000</v>
       </c>
       <c r="N29">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="O29">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="P29">
-        <v>62800</v>
+        <v>27100</v>
       </c>
     </row>
     <row r="30">
@@ -1484,23 +1484,23 @@
         <v>-</v>
       </c>
       <c r="C30">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>0.1</v>
+      </c>
+      <c r="E30">
+        <v>1.2658227848101267</v>
+      </c>
+      <c r="F30">
+        <v>7.9</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30">
         <v>7.85</v>
       </c>
-      <c r="D30">
-        <v>0.05</v>
-      </c>
-      <c r="E30">
-        <v>0.6410256410256411</v>
-      </c>
-      <c r="F30">
-        <v>7.85</v>
-      </c>
-      <c r="G30">
-        <v>7.9</v>
-      </c>
-      <c r="H30">
-        <v>7.8</v>
-      </c>
       <c r="I30">
         <v>0</v>
       </c>
@@ -1508,22 +1508,22 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>1972647</v>
+        <v>10279852</v>
       </c>
       <c r="L30">
-        <v>15431.817949999999</v>
+        <v>81970.08775</v>
       </c>
       <c r="M30">
-        <v>539400</v>
+        <v>437700</v>
       </c>
       <c r="N30">
-        <v>7.8</v>
+        <v>7.95</v>
       </c>
       <c r="O30">
-        <v>7.85</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>178800</v>
+        <v>132200</v>
       </c>
     </row>
     <row r="31">
@@ -1534,46 +1534,46 @@
         <v>-</v>
       </c>
       <c r="C31">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>-0.6172839506172839</v>
       </c>
       <c r="F31">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="G31">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="H31">
+        <v>16</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>4381392</v>
+      </c>
+      <c r="L31">
+        <v>70741.9954</v>
+      </c>
+      <c r="M31">
+        <v>580600</v>
+      </c>
+      <c r="N31">
+        <v>16.1</v>
+      </c>
+      <c r="O31">
         <v>16.2</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>1943974</v>
-      </c>
-      <c r="L31">
-        <v>31713.3482</v>
-      </c>
-      <c r="M31">
-        <v>727500</v>
-      </c>
-      <c r="N31">
-        <v>16.2</v>
-      </c>
-      <c r="O31">
-        <v>16.3</v>
-      </c>
       <c r="P31">
-        <v>310000</v>
+        <v>807600</v>
       </c>
     </row>
     <row r="32">
@@ -1587,19 +1587,19 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>2.479338842975207</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="G32">
-        <v>31</v>
+        <v>31.25</v>
       </c>
       <c r="H32">
-        <v>30.5</v>
+        <v>30.75</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1608,13 +1608,13 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>1326990</v>
+        <v>1864108</v>
       </c>
       <c r="L32">
-        <v>40796.9215</v>
+        <v>57752.77575</v>
       </c>
       <c r="M32">
-        <v>209300</v>
+        <v>385200</v>
       </c>
       <c r="N32">
         <v>30.75</v>
@@ -1623,7 +1623,7 @@
         <v>31</v>
       </c>
       <c r="P32">
-        <v>536800</v>
+        <v>96800</v>
       </c>
     </row>
     <row r="33">
@@ -1634,19 +1634,19 @@
         <v>-</v>
       </c>
       <c r="C33">
+        <v>8.2</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>8.2</v>
+      </c>
+      <c r="G33">
         <v>8.25</v>
-      </c>
-      <c r="D33">
-        <v>0.1</v>
-      </c>
-      <c r="E33">
-        <v>1.2269938650306749</v>
-      </c>
-      <c r="F33">
-        <v>8.15</v>
-      </c>
-      <c r="G33">
-        <v>8.3</v>
       </c>
       <c r="H33">
         <v>8.15</v>
@@ -1658,22 +1658,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>1985830</v>
+        <v>1051610</v>
       </c>
       <c r="L33">
-        <v>16367.6025</v>
+        <v>8626.647</v>
       </c>
       <c r="M33">
-        <v>821700</v>
+        <v>2605500</v>
       </c>
       <c r="N33">
         <v>8.2</v>
       </c>
       <c r="O33">
-        <v>8.3</v>
+        <v>8.25</v>
       </c>
       <c r="P33">
-        <v>1219100</v>
+        <v>1124700</v>
       </c>
     </row>
     <row r="34">
@@ -1734,22 +1734,22 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="D35">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="E35">
-        <v>0.6802721088435374</v>
+        <v>5.405405405405405</v>
       </c>
       <c r="F35">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="G35">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="H35">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1758,22 +1758,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>200</v>
+        <v>2595</v>
       </c>
       <c r="L35">
-        <v>1.48</v>
+        <v>20.443450000000002</v>
       </c>
       <c r="M35">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="N35">
         <v>7.4</v>
       </c>
       <c r="O35">
-        <v>7.65</v>
+        <v>7.55</v>
       </c>
       <c r="P35">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
@@ -1793,37 +1793,37 @@
         <v>0.6211180124223602</v>
       </c>
       <c r="F36">
-        <v>8.1</v>
+        <v>8.05</v>
       </c>
       <c r="G36">
         <v>8.15</v>
       </c>
       <c r="H36">
+        <v>8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>3759691</v>
+      </c>
+      <c r="L36">
+        <v>30312.5005</v>
+      </c>
+      <c r="M36">
+        <v>178500</v>
+      </c>
+      <c r="N36">
         <v>8.05</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>1728396</v>
-      </c>
-      <c r="L36">
-        <v>14003.966849999999</v>
-      </c>
-      <c r="M36">
-        <v>458900</v>
-      </c>
-      <c r="N36">
+      <c r="O36">
         <v>8.1</v>
       </c>
-      <c r="O36">
-        <v>8.15</v>
-      </c>
       <c r="P36">
-        <v>449900</v>
+        <v>88100</v>
       </c>
     </row>
     <row r="37">
@@ -1834,46 +1834,46 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="D37">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E37">
-        <v>1.7094017094017093</v>
+        <v>-2.5</v>
       </c>
       <c r="F37">
+        <v>12</v>
+      </c>
+      <c r="G37">
+        <v>12.1</v>
+      </c>
+      <c r="H37">
+        <v>11.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>6565095</v>
+      </c>
+      <c r="L37">
+        <v>77325.6161</v>
+      </c>
+      <c r="M37">
+        <v>801500</v>
+      </c>
+      <c r="N37">
         <v>11.7</v>
       </c>
-      <c r="G37">
-        <v>12</v>
-      </c>
-      <c r="H37">
-        <v>11.7</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>2575189</v>
-      </c>
-      <c r="L37">
-        <v>30484.8</v>
-      </c>
-      <c r="M37">
-        <v>44400</v>
-      </c>
-      <c r="N37">
-        <v>11.9</v>
-      </c>
       <c r="O37">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="P37">
-        <v>833400</v>
+        <v>357100</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (8).xlsx
+++ b/Excel/StockQuotation (8).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>07/02/23 23:30:43</v>
+        <v>08/02/23 20:06:34</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>372.26</v>
+        <v>373.11</v>
       </c>
       <c r="B7" t="str">
-        <v>-1.5 (-0.4013%)</v>
+        <v>0.85 (0.2283%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>374.2</v>
+        <v>374.59</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>370.84</v>
+        <v>371.09</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>415445555</v>
+        <v>226487487</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>3395647413.95</v>
+        <v>2855024894.04</v>
       </c>
     </row>
     <row r="9">
@@ -534,46 +534,46 @@
         <v>-</v>
       </c>
       <c r="C11">
+        <v>3.04</v>
+      </c>
+      <c r="D11">
+        <v>-0.04</v>
+      </c>
+      <c r="E11">
+        <v>-1.2987012987012987</v>
+      </c>
+      <c r="F11">
         <v>3.08</v>
       </c>
-      <c r="D11">
-        <v>-0.02</v>
-      </c>
-      <c r="E11">
-        <v>-0.6451612903225806</v>
-      </c>
-      <c r="F11">
+      <c r="G11">
         <v>3.1</v>
       </c>
-      <c r="G11">
-        <v>3.12</v>
-      </c>
       <c r="H11">
+        <v>3.04</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>35912008</v>
+      </c>
+      <c r="L11">
+        <v>110055.06809999999</v>
+      </c>
+      <c r="M11">
+        <v>10794000</v>
+      </c>
+      <c r="N11">
+        <v>3.04</v>
+      </c>
+      <c r="O11">
         <v>3.06</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>47860704</v>
-      </c>
-      <c r="L11">
-        <v>148095.61584</v>
-      </c>
-      <c r="M11">
-        <v>10938600</v>
-      </c>
-      <c r="N11">
-        <v>3.06</v>
-      </c>
-      <c r="O11">
-        <v>3.08</v>
-      </c>
       <c r="P11">
-        <v>307300</v>
+        <v>1584000</v>
       </c>
     </row>
     <row r="12">
@@ -584,46 +584,46 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>73.5</v>
+        <v>74</v>
       </c>
       <c r="D12">
-        <v>-0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E12">
-        <v>-0.3389830508474576</v>
+        <v>0.6802721088435374</v>
       </c>
       <c r="F12">
         <v>73.5</v>
       </c>
       <c r="G12">
-        <v>74</v>
+        <v>74.25</v>
       </c>
       <c r="H12">
         <v>73.25</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>261700</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>19267.6625</v>
       </c>
       <c r="K12">
-        <v>19882884</v>
+        <v>20316385</v>
       </c>
       <c r="L12">
-        <v>1462189.4985</v>
+        <v>1499172.9605</v>
       </c>
       <c r="M12">
-        <v>5942900</v>
+        <v>1223100</v>
       </c>
       <c r="N12">
-        <v>73.5</v>
+        <v>73.75</v>
       </c>
       <c r="O12">
-        <v>73.75</v>
+        <v>74</v>
       </c>
       <c r="P12">
-        <v>439300</v>
+        <v>578900</v>
       </c>
     </row>
     <row r="13">
@@ -634,22 +634,22 @@
         <v>-</v>
       </c>
       <c r="C13">
+        <v>1.84</v>
+      </c>
+      <c r="D13">
+        <v>-0.01</v>
+      </c>
+      <c r="E13">
+        <v>-0.5405405405405406</v>
+      </c>
+      <c r="F13">
         <v>1.85</v>
-      </c>
-      <c r="D13">
-        <v>0.03</v>
-      </c>
-      <c r="E13">
-        <v>1.6483516483516483</v>
-      </c>
-      <c r="F13">
-        <v>1.82</v>
       </c>
       <c r="G13">
         <v>1.85</v>
       </c>
       <c r="H13">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -658,22 +658,22 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>173315</v>
+        <v>64903</v>
       </c>
       <c r="L13">
-        <v>319.28445</v>
+        <v>119.79358</v>
       </c>
       <c r="M13">
-        <v>16600</v>
+        <v>121200</v>
       </c>
       <c r="N13">
+        <v>1.83</v>
+      </c>
+      <c r="O13">
         <v>1.84</v>
       </c>
-      <c r="O13">
-        <v>1.85</v>
-      </c>
       <c r="P13">
-        <v>10500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="14">
@@ -684,23 +684,23 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="D14">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="E14">
-        <v>7.317073170731708</v>
+        <v>-2.272727272727273</v>
       </c>
       <c r="F14">
+        <v>0.45</v>
+      </c>
+      <c r="G14">
+        <v>0.45</v>
+      </c>
+      <c r="H14">
         <v>0.42</v>
       </c>
-      <c r="G14">
-        <v>0.46</v>
-      </c>
-      <c r="H14">
-        <v>0.41</v>
-      </c>
       <c r="I14">
         <v>0</v>
       </c>
@@ -708,22 +708,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>158162818</v>
+        <v>43298036</v>
       </c>
       <c r="L14">
-        <v>69981.95081000001</v>
+        <v>18857.77894</v>
       </c>
       <c r="M14">
-        <v>10628000</v>
+        <v>19441200</v>
       </c>
       <c r="N14">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="O14">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="P14">
-        <v>7799100</v>
+        <v>4855600</v>
       </c>
     </row>
     <row r="15">
@@ -734,46 +734,46 @@
         <v>-</v>
       </c>
       <c r="C15">
+        <v>14.6</v>
+      </c>
+      <c r="D15">
+        <v>-0.2</v>
+      </c>
+      <c r="E15">
+        <v>-1.3513513513513513</v>
+      </c>
+      <c r="F15">
         <v>14.8</v>
       </c>
-      <c r="D15">
-        <v>0.3</v>
-      </c>
-      <c r="E15">
-        <v>2.0689655172413794</v>
-      </c>
-      <c r="F15">
+      <c r="G15">
+        <v>14.8</v>
+      </c>
+      <c r="H15">
+        <v>14.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>3813346</v>
+      </c>
+      <c r="L15">
+        <v>55477.7679</v>
+      </c>
+      <c r="M15">
+        <v>61800</v>
+      </c>
+      <c r="N15">
+        <v>14.5</v>
+      </c>
+      <c r="O15">
         <v>14.6</v>
       </c>
-      <c r="G15">
-        <v>14.9</v>
-      </c>
-      <c r="H15">
-        <v>14.2</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>9344082</v>
-      </c>
-      <c r="L15">
-        <v>136141.3224</v>
-      </c>
-      <c r="M15">
-        <v>153200</v>
-      </c>
-      <c r="N15">
-        <v>14.7</v>
-      </c>
-      <c r="O15">
-        <v>14.8</v>
-      </c>
       <c r="P15">
-        <v>137100</v>
+        <v>22600</v>
       </c>
     </row>
     <row r="16">
@@ -784,19 +784,19 @@
         <v>-</v>
       </c>
       <c r="C16">
+        <v>9.65</v>
+      </c>
+      <c r="D16">
+        <v>0.05</v>
+      </c>
+      <c r="E16">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="F16">
         <v>9.6</v>
       </c>
-      <c r="D16">
-        <v>-0.15</v>
-      </c>
-      <c r="E16">
-        <v>-1.5384615384615385</v>
-      </c>
-      <c r="F16">
-        <v>9.7</v>
-      </c>
       <c r="G16">
-        <v>9.75</v>
+        <v>9.65</v>
       </c>
       <c r="H16">
         <v>9.55</v>
@@ -808,13 +808,13 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>58793587</v>
+        <v>37282411</v>
       </c>
       <c r="L16">
-        <v>565334.3098500001</v>
+        <v>358143.69605</v>
       </c>
       <c r="M16">
-        <v>1211000</v>
+        <v>5826400</v>
       </c>
       <c r="N16">
         <v>9.6</v>
@@ -823,7 +823,7 @@
         <v>9.65</v>
       </c>
       <c r="P16">
-        <v>3215400</v>
+        <v>1946600</v>
       </c>
     </row>
     <row r="17">
@@ -834,46 +834,46 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>-3.1578947368421053</v>
       </c>
       <c r="F17">
         <v>0.95</v>
       </c>
       <c r="G17">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="H17">
+        <v>0.92</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>10235937</v>
+      </c>
+      <c r="L17">
+        <v>9557.64308</v>
+      </c>
+      <c r="M17">
+        <v>1381900</v>
+      </c>
+      <c r="N17">
+        <v>0.92</v>
+      </c>
+      <c r="O17">
         <v>0.94</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>11804761</v>
-      </c>
-      <c r="L17">
-        <v>11197.88796</v>
-      </c>
-      <c r="M17">
-        <v>1582900</v>
-      </c>
-      <c r="N17">
-        <v>0.94</v>
-      </c>
-      <c r="O17">
-        <v>0.95</v>
-      </c>
       <c r="P17">
-        <v>623000</v>
+        <v>153400</v>
       </c>
     </row>
     <row r="18">
@@ -884,19 +884,19 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="D18">
         <v>-0.05</v>
       </c>
       <c r="E18">
-        <v>-0.6024096385542169</v>
+        <v>-0.6060606060606061</v>
       </c>
       <c r="F18">
         <v>8.3</v>
       </c>
       <c r="G18">
-        <v>8.4</v>
+        <v>8.3</v>
       </c>
       <c r="H18">
         <v>8.2</v>
@@ -908,22 +908,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>52782066</v>
+        <v>23116540</v>
       </c>
       <c r="L18">
-        <v>436595.46095</v>
+        <v>190510.177</v>
       </c>
       <c r="M18">
-        <v>267700</v>
+        <v>6632600</v>
       </c>
       <c r="N18">
+        <v>8.2</v>
+      </c>
+      <c r="O18">
         <v>8.25</v>
       </c>
-      <c r="O18">
-        <v>8.3</v>
-      </c>
       <c r="P18">
-        <v>1769900</v>
+        <v>1478800</v>
       </c>
     </row>
     <row r="19">
@@ -934,13 +934,13 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>-0.5128205128205128</v>
       </c>
       <c r="F19">
         <v>3.9</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>1226642</v>
+        <v>1958303</v>
       </c>
       <c r="L19">
-        <v>4779.416139999999</v>
+        <v>7611.345740000001</v>
       </c>
       <c r="M19">
-        <v>868800</v>
+        <v>718700</v>
       </c>
       <c r="N19">
         <v>3.88</v>
@@ -973,7 +973,7 @@
         <v>3.9</v>
       </c>
       <c r="P19">
-        <v>308700</v>
+        <v>256800</v>
       </c>
     </row>
     <row r="20">
@@ -984,46 +984,46 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>-2.3076923076923075</v>
       </c>
       <c r="F20">
         <v>13</v>
       </c>
       <c r="G20">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="H20">
+        <v>12.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>926947</v>
+      </c>
+      <c r="L20">
+        <v>11869.731800000001</v>
+      </c>
+      <c r="M20">
+        <v>60300</v>
+      </c>
+      <c r="N20">
+        <v>12.7</v>
+      </c>
+      <c r="O20">
         <v>12.8</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>1248511</v>
-      </c>
-      <c r="L20">
-        <v>16126.752</v>
-      </c>
-      <c r="M20">
-        <v>60000</v>
-      </c>
-      <c r="N20">
-        <v>12.9</v>
-      </c>
-      <c r="O20">
-        <v>13</v>
-      </c>
       <c r="P20">
-        <v>6900</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="21">
@@ -1034,22 +1034,22 @@
         <v>-</v>
       </c>
       <c r="C21">
+        <v>14.5</v>
+      </c>
+      <c r="D21">
+        <v>-0.4</v>
+      </c>
+      <c r="E21">
+        <v>-2.684563758389262</v>
+      </c>
+      <c r="F21">
+        <v>14.8</v>
+      </c>
+      <c r="G21">
         <v>14.9</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>15</v>
-      </c>
-      <c r="G21">
-        <v>15.2</v>
-      </c>
       <c r="H21">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1058,22 +1058,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>2849592</v>
+        <v>3075851</v>
       </c>
       <c r="L21">
-        <v>42696.6472</v>
+        <v>45153.07</v>
       </c>
       <c r="M21">
-        <v>142800</v>
+        <v>208400</v>
       </c>
       <c r="N21">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="O21">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="P21">
-        <v>114900</v>
+        <v>19100</v>
       </c>
     </row>
     <row r="22">
@@ -1084,46 +1084,46 @@
         <v>-</v>
       </c>
       <c r="C22">
+        <v>20.4</v>
+      </c>
+      <c r="D22">
+        <v>-0.3</v>
+      </c>
+      <c r="E22">
+        <v>-1.4492753623188406</v>
+      </c>
+      <c r="F22">
         <v>20.7</v>
       </c>
-      <c r="D22">
-        <v>-0.2</v>
-      </c>
-      <c r="E22">
-        <v>-0.9569377990430622</v>
-      </c>
-      <c r="F22">
-        <v>20.8</v>
-      </c>
       <c r="G22">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="H22">
+        <v>19.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>7581343</v>
+      </c>
+      <c r="L22">
+        <v>153631.8931</v>
+      </c>
+      <c r="M22">
+        <v>479600</v>
+      </c>
+      <c r="N22">
+        <v>20.4</v>
+      </c>
+      <c r="O22">
         <v>20.5</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>5033514</v>
-      </c>
-      <c r="L22">
-        <v>104421.0835</v>
-      </c>
-      <c r="M22">
-        <v>167300</v>
-      </c>
-      <c r="N22">
-        <v>20.6</v>
-      </c>
-      <c r="O22">
-        <v>20.7</v>
-      </c>
       <c r="P22">
-        <v>10300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="23">
@@ -1134,46 +1134,46 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="D23">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E23">
-        <v>-1.6129032258064515</v>
+        <v>-1.092896174863388</v>
       </c>
       <c r="F23">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="G23">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="H23">
+        <v>18.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>2402994</v>
+      </c>
+      <c r="L23">
+        <v>43820.721</v>
+      </c>
+      <c r="M23">
+        <v>163700</v>
+      </c>
+      <c r="N23">
+        <v>18.1</v>
+      </c>
+      <c r="O23">
         <v>18.2</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>2231293</v>
-      </c>
-      <c r="L23">
-        <v>40973.5248</v>
-      </c>
-      <c r="M23">
-        <v>130400</v>
-      </c>
-      <c r="N23">
-        <v>18.3</v>
-      </c>
-      <c r="O23">
-        <v>18.4</v>
-      </c>
       <c r="P23">
-        <v>30900</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="24">
@@ -1184,13 +1184,13 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="D24">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="E24">
-        <v>2.0408163265306123</v>
+        <v>-2</v>
       </c>
       <c r="F24">
         <v>0.5</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>2311200</v>
+        <v>2877382</v>
       </c>
       <c r="L24">
-        <v>1153.77992</v>
+        <v>1411.1759</v>
       </c>
       <c r="M24">
-        <v>1815300</v>
+        <v>2173600</v>
       </c>
       <c r="N24">
+        <v>0.48</v>
+      </c>
+      <c r="O24">
         <v>0.49</v>
       </c>
-      <c r="O24">
-        <v>0.5</v>
-      </c>
       <c r="P24">
-        <v>3426700</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="25">
@@ -1233,44 +1233,44 @@
       <c r="B25" t="str">
         <v>-</v>
       </c>
-      <c r="C25">
-        <v>248</v>
-      </c>
-      <c r="D25">
+      <c r="C25" t="str">
+        <v>-</v>
+      </c>
+      <c r="D25" t="str">
+        <v>-</v>
+      </c>
+      <c r="E25" t="str">
+        <v>-</v>
+      </c>
+      <c r="F25" t="str">
+        <v>-</v>
+      </c>
+      <c r="G25" t="str">
+        <v>-</v>
+      </c>
+      <c r="H25" t="str">
+        <v>-</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>2</v>
       </c>
-      <c r="E25">
-        <v>0.8130081300813008</v>
-      </c>
-      <c r="F25">
-        <v>248</v>
-      </c>
-      <c r="G25">
-        <v>248</v>
-      </c>
-      <c r="H25">
-        <v>248</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>101</v>
-      </c>
       <c r="L25">
-        <v>25.048</v>
+        <v>0.497</v>
       </c>
       <c r="M25">
         <v>100</v>
       </c>
       <c r="N25">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O25">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -1284,19 +1284,19 @@
         <v>-</v>
       </c>
       <c r="C26">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="D26">
         <v>-0.03</v>
       </c>
       <c r="E26">
-        <v>-1.530612244897959</v>
+        <v>-1.5544041450777202</v>
       </c>
       <c r="F26">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G26">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="H26">
         <v>1.9</v>
@@ -1308,22 +1308,22 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>12027803</v>
+        <v>1611010</v>
       </c>
       <c r="L26">
-        <v>23381.7872</v>
+        <v>3073.2932</v>
       </c>
       <c r="M26">
-        <v>299700</v>
+        <v>33100</v>
       </c>
       <c r="N26">
+        <v>1.9</v>
+      </c>
+      <c r="O26">
         <v>1.91</v>
       </c>
-      <c r="O26">
-        <v>1.93</v>
-      </c>
       <c r="P26">
-        <v>155300</v>
+        <v>105300</v>
       </c>
     </row>
     <row r="27">
@@ -1384,16 +1384,16 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="D28">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E28">
-        <v>1.1363636363636365</v>
+        <v>-0.5617977528089888</v>
       </c>
       <c r="F28">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="G28">
         <v>3.58</v>
@@ -1408,22 +1408,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>1176916</v>
+        <v>1881824</v>
       </c>
       <c r="L28">
-        <v>4173.16084</v>
+        <v>6675.10318</v>
       </c>
       <c r="M28">
-        <v>93000</v>
+        <v>357800</v>
       </c>
       <c r="N28">
+        <v>3.52</v>
+      </c>
+      <c r="O28">
         <v>3.54</v>
       </c>
-      <c r="O28">
-        <v>3.56</v>
-      </c>
       <c r="P28">
-        <v>156500</v>
+        <v>237500</v>
       </c>
     </row>
     <row r="29">
@@ -1434,22 +1434,22 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="D29">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E29">
-        <v>-1.8691588785046729</v>
+        <v>-2.857142857142857</v>
       </c>
       <c r="F29">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G29">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1458,22 +1458,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>631423</v>
+        <v>206252</v>
       </c>
       <c r="L29">
-        <v>1310.81764</v>
+        <v>428.03652</v>
       </c>
       <c r="M29">
-        <v>24000</v>
+        <v>43900</v>
       </c>
       <c r="N29">
+        <v>2.04</v>
+      </c>
+      <c r="O29">
         <v>2.08</v>
       </c>
-      <c r="O29">
-        <v>2.1</v>
-      </c>
       <c r="P29">
-        <v>27100</v>
+        <v>52100</v>
       </c>
     </row>
     <row r="30">
@@ -1487,19 +1487,19 @@
         <v>8</v>
       </c>
       <c r="D30">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>1.2658227848101267</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>7.9</v>
+        <v>8.05</v>
       </c>
       <c r="G30">
-        <v>8</v>
+        <v>8.05</v>
       </c>
       <c r="H30">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1508,13 +1508,13 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>10279852</v>
+        <v>12248999</v>
       </c>
       <c r="L30">
-        <v>81970.08775</v>
+        <v>96951.0574</v>
       </c>
       <c r="M30">
-        <v>437700</v>
+        <v>43300</v>
       </c>
       <c r="N30">
         <v>7.95</v>
@@ -1523,7 +1523,7 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>132200</v>
+        <v>672300</v>
       </c>
     </row>
     <row r="31">
@@ -1537,16 +1537,16 @@
         <v>16.1</v>
       </c>
       <c r="D31">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>-0.6172839506172839</v>
+        <v>0</v>
       </c>
       <c r="F31">
+        <v>16</v>
+      </c>
+      <c r="G31">
         <v>16.2</v>
-      </c>
-      <c r="G31">
-        <v>16.4</v>
       </c>
       <c r="H31">
         <v>16</v>
@@ -1558,13 +1558,13 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>4381392</v>
+        <v>3321948</v>
       </c>
       <c r="L31">
-        <v>70741.9954</v>
+        <v>53462.680799999995</v>
       </c>
       <c r="M31">
-        <v>580600</v>
+        <v>47800</v>
       </c>
       <c r="N31">
         <v>16.1</v>
@@ -1573,7 +1573,7 @@
         <v>16.2</v>
       </c>
       <c r="P31">
-        <v>807600</v>
+        <v>513700</v>
       </c>
     </row>
     <row r="32">
@@ -1584,13 +1584,13 @@
         <v>-</v>
       </c>
       <c r="C32">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>-1.6129032258064515</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -1599,31 +1599,31 @@
         <v>31.25</v>
       </c>
       <c r="H32">
+        <v>30.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>2338011</v>
+      </c>
+      <c r="L32">
+        <v>71924.69825</v>
+      </c>
+      <c r="M32">
+        <v>547600</v>
+      </c>
+      <c r="N32">
+        <v>30.5</v>
+      </c>
+      <c r="O32">
         <v>30.75</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>1864108</v>
-      </c>
-      <c r="L32">
-        <v>57752.77575</v>
-      </c>
-      <c r="M32">
-        <v>385200</v>
-      </c>
-      <c r="N32">
-        <v>30.75</v>
-      </c>
-      <c r="O32">
-        <v>31</v>
-      </c>
       <c r="P32">
-        <v>96800</v>
+        <v>42900</v>
       </c>
     </row>
     <row r="33">
@@ -1658,22 +1658,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>1051610</v>
+        <v>1406125</v>
       </c>
       <c r="L33">
-        <v>8626.647</v>
+        <v>11531.1684</v>
       </c>
       <c r="M33">
-        <v>2605500</v>
+        <v>3618200</v>
       </c>
       <c r="N33">
+        <v>8.15</v>
+      </c>
+      <c r="O33">
         <v>8.2</v>
       </c>
-      <c r="O33">
-        <v>8.25</v>
-      </c>
       <c r="P33">
-        <v>1124700</v>
+        <v>176400</v>
       </c>
     </row>
     <row r="34">
@@ -1734,22 +1734,22 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D35">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="E35">
-        <v>5.405405405405405</v>
+        <v>-5.128205128205129</v>
       </c>
       <c r="F35">
-        <v>7.9</v>
+        <v>7.35</v>
       </c>
       <c r="G35">
-        <v>7.9</v>
+        <v>7.55</v>
       </c>
       <c r="H35">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1758,10 +1758,10 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>2595</v>
+        <v>2010</v>
       </c>
       <c r="L35">
-        <v>20.443450000000002</v>
+        <v>14.96375</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -1784,46 +1784,46 @@
         <v>-</v>
       </c>
       <c r="C36">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <v>-0.1</v>
+      </c>
+      <c r="E36">
+        <v>-1.2345679012345678</v>
+      </c>
+      <c r="F36">
         <v>8.1</v>
       </c>
-      <c r="D36">
-        <v>0.05</v>
-      </c>
-      <c r="E36">
-        <v>0.6211180124223602</v>
-      </c>
-      <c r="F36">
+      <c r="G36">
+        <v>8.1</v>
+      </c>
+      <c r="H36">
+        <v>7.95</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>4719758</v>
+      </c>
+      <c r="L36">
+        <v>37730.91895000001</v>
+      </c>
+      <c r="M36">
+        <v>5300</v>
+      </c>
+      <c r="N36">
+        <v>8</v>
+      </c>
+      <c r="O36">
         <v>8.05</v>
       </c>
-      <c r="G36">
-        <v>8.15</v>
-      </c>
-      <c r="H36">
-        <v>8</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>3759691</v>
-      </c>
-      <c r="L36">
-        <v>30312.5005</v>
-      </c>
-      <c r="M36">
-        <v>178500</v>
-      </c>
-      <c r="N36">
-        <v>8.05</v>
-      </c>
-      <c r="O36">
-        <v>8.1</v>
-      </c>
       <c r="P36">
-        <v>88100</v>
+        <v>86100</v>
       </c>
     </row>
     <row r="37">
@@ -1834,22 +1834,22 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="D37">
         <v>-0.3</v>
       </c>
       <c r="E37">
-        <v>-2.5</v>
+        <v>-2.5641025641025643</v>
       </c>
       <c r="F37">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="G37">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="H37">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1858,22 +1858,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>6565095</v>
+        <v>5889162</v>
       </c>
       <c r="L37">
-        <v>77325.6161</v>
+        <v>67839.6539</v>
       </c>
       <c r="M37">
-        <v>801500</v>
+        <v>80800</v>
       </c>
       <c r="N37">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="O37">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="P37">
-        <v>357100</v>
+        <v>185700</v>
       </c>
     </row>
   </sheetData>
